--- a/docs/engineering-change/samples/t28-2025-07-import-bundle.xlsx
+++ b/docs/engineering-change/samples/t28-2025-07-import-bundle.xlsx
@@ -371,10 +371,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -797,15 +797,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="108" customHeight="1">
+    <row r="2" ht="148" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>一本 Excel、五种改法。后面三张表和日常导入模板相同。基地 青岛，顾客 奇瑞公司，投产清单版本 D/00。先写变更类型和原来的交货总成，再写这一次动到的零件。总成名称、零件名称变更前后相同，各只一列。零件层级=总成时零件名称空。材料清单只写变化的行，没变的零件不要抄。完成停止：变更后总成空，材料清单不写这个总成。此件不装：总成还交货，变更前总成/变更后总成 AA→AB，变更后零件空；该行用量写 0、备注含「此件不装」。增加零件：加在原来的总成上，不是新开一棵总成。变更前总成/变更后总成 AA→AB，变更前零件空、变更后零件写新号，用量 &gt; 0。</t>
+          <t>一本对照样表，两种填法订在一起。后面三张表和日常导入模板相同。基地 青岛，顾客 奇瑞公司，投产清单版本 D/00。上五行：五种改法，一行一个交货总成（完成停止 / 一级改图 / 二级改图 / 此件不装 / 增加零件）。下四行：同一个后围总成 501008897AA → 501008897AB 同时四种改法；变更前总成、变更后总成、总成名称上下合并，只需填一次。先写原来的交货总成，再写变更类型和这一次动到的零件。材料清单只写变化的行；改图二级写出整条链。没变的零件不要抄。完成停止：变更后总成空，材料清单不写这个总成。此件不装：变更后零件空；用量 0、备注含「此件不装」。增加零件：加在原来的总成上；变更前零件空、变更后零件写新号。日常按交货总成拆开上传；整本对照不必一次进系统。</t>
         </is>
       </c>
     </row>
@@ -839,22 +839,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>变更前总成</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>变更后总成</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>总成名称</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>变更类型</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>变更前总成</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>变更后总成</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>总成名称</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -891,18 +891,18 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>501009533AA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>发盖左铰链安装支架总成</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>完成停止</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>501009533AA</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>发盖左铰链安装支架总成</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -919,22 +919,22 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>501006873AA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>501006873AB</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>流水槽加强梁总成</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>改图</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>501006873AA</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>501006873AB</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>流水槽加强梁总成</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -963,22 +963,22 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>501009144AA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>501009144AB</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>后防撞梁总成</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>改图</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>501009144AA</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>501009144AB</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>后防撞梁总成</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1005,24 +1005,24 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>501008897AA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>501008897AB</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>后围总成</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>此件不装</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>501008897AA</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>501008897AB</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>后围总成</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1043,51 +1043,186 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>501007029AA</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>501007029AB</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>中通道左后纵梁总成</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>增加零件</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>501007029AA</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>501007029AB</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>中通道左后纵梁总成</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>一级</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>501007040AA</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>中通道后纵梁加强板</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>501008897AA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>501008897AB</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>后围总成</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>改图</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>501008899AA</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>501008899AB</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>后围内板</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>改图</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>二级</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>501008901AA</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>501008901AB</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>后围左连接板</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>此件不装</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>504000341AA</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>左D柱下结构增强胶块</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>增加零件</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>501008903AA</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>后围加强板</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A5:A9"/>
+  <mergeCells count="7">
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="D10:D13"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="A5:A13"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="E10:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1310,10 +1445,8 @@
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F5" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -1388,157 +1521,151 @@
       <c r="W5" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>ACA611</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>501008897AB</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>后围总成</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>焊点：99 凸焊：7 涂胶：1550mm</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>ACA611001</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>501008899AB</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>后围内板</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>焊点：99 凸焊：7 涂胶：1550mm</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>ACA611009</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>504000341AA</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>左D柱下结构增强胶块</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="P6" s="11" t="n"/>
+      <c r="Q6" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>PA6+GF36</t>
-        </is>
-      </c>
-      <c r="S6" s="12" t="inlineStr">
-        <is>
-          <t>发泡料（环氧树脂等）</t>
-        </is>
-      </c>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="12" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="V6" s="12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>此件不装</t>
-        </is>
-      </c>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>DC01</t>
+        </is>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>T=0.7</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="n"/>
+      <c r="U6" s="11" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>ACA612</t>
+          <t>ACA611</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>501009144AB</t>
+          <t>501008897AB</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>后防撞梁总成</t>
+          <t>后围总成</t>
         </is>
       </c>
       <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>焊点：99 凸焊：7 涂胶：1550mm</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>ACA611N01</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>501008901AB-1</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>后围左连接板分总成</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>焊缝：58条（1392mm) 凸焊：4</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>ACA612N01</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>501009122AB-1</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>后保下安装支架总成</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>凸焊:1</t>
+          <t>凸焊：2</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1548,12 +1675,12 @@
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>501009122AB</t>
+          <t>501008901AB</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>后保下安装支架</t>
+          <t>后围左连接板</t>
         </is>
       </c>
       <c r="P7" s="11" t="n"/>
@@ -1564,129 +1691,415 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>HC180YD+Z</t>
+          <t>HC180Y</t>
         </is>
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>T=1.0</t>
+          <t>T=1.5</t>
         </is>
       </c>
       <c r="T7" s="11" t="n"/>
       <c r="U7" s="11" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>凸焊总成供货</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>ACA611</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>501008897AB</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>后围总成</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>焊点：99 凸焊：7 涂胶：1550mm</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>ACA611009</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>504000341AA</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>左D柱下结构增强胶块</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
+        <is>
+          <t>PA6+GF36</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>发泡料（环氧树脂等）</t>
+        </is>
+      </c>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="V8" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
+        <is>
+          <t>此件不装</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>ACA611</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>501008897AB</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>后围总成</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>焊点：99 凸焊：7 涂胶：1550mm</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>ACA611011</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>501008903AA</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>后围加强板</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>HC260Y</t>
+        </is>
+      </c>
+      <c r="S9" s="13" t="inlineStr">
+        <is>
+          <t>T=1.4</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="W9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>ACA612</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>501009144AB</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>后防撞梁总成</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>焊缝：58条（1392mm) 凸焊：4</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>ACA612N01</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>501009122AB-1</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>后保下安装支架总成</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>凸焊:1</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>501009122AB</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>后保下安装支架</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="n"/>
+      <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="11" t="inlineStr">
+        <is>
+          <t>HC180YD+Z</t>
+        </is>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>T=1.0</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="n"/>
+      <c r="U10" s="11" t="n">
         <v>0.041</v>
       </c>
-      <c r="V7" s="11" t="inlineStr">
+      <c r="V10" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>凸焊总成供货</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="13" t="n">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>ACA613</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>501007029AB</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>中通道左后纵梁总成</t>
         </is>
       </c>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>焊点：7 焊缝：2条（52mm）</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>ACA613002</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>501007040AA</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>中通道后纵梁加强板</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>焊点：7 焊缝：2条（52mm）</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>ACA613002</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>501007040AA</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>中通道后纵梁加强板</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R11" s="13" t="inlineStr">
         <is>
           <t>HC340/590DP</t>
         </is>
       </c>
-      <c r="S8" s="13" t="inlineStr">
+      <c r="S11" s="13" t="inlineStr">
         <is>
           <t>T=1.0</t>
         </is>
       </c>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n">
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="13" t="n">
         <v>0.235</v>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V11" s="13" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="W8" s="13" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+      <c r="W11" s="13" t="n"/>
+    </row>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
@@ -2083,13 +2496,13 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
           <t>长（卷料宽）</t>
@@ -2135,9 +2548,9 @@
           <t>模具套数</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -2334,119 +2747,431 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>501008899AB</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>后围内板</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>DC01</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>370</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" s="11" t="n"/>
       <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>条料</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="11" t="n"/>
-      <c r="S10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
+      <c r="R10" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>铸造模</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>TR+CTR+CPI</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
+      <c r="R11" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="S11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" s="11" t="n"/>
-      <c r="R12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
+      <c r="R12" s="11" t="n">
+        <v>630</v>
+      </c>
+      <c r="S12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>OP40</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>TR+CTR+PI+CPI</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
-      <c r="P14" s="11" t="n"/>
+      <c r="R13" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="S13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>501008901AB</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>后围左连接板</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>HC180Y</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>860</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>520</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>条料</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="11" t="n"/>
-      <c r="R14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
+      <c r="R14" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>铸造模</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n"/>
-    </row>
-    <row r="16">
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="11" t="n"/>
-      <c r="P16" s="11" t="n"/>
+      <c r="R15" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="S15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>TR+C/TR+SEP</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" s="11" t="n"/>
-      <c r="R16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n"/>
+      <c r="R16" s="11" t="n">
+        <v>630</v>
+      </c>
+      <c r="S16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>OP40</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>FL+U/FL+RST</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="11" t="n"/>
-      <c r="P18" s="11" t="n"/>
+      <c r="R17" s="11" t="n">
+        <v>630</v>
+      </c>
+      <c r="S17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>OP50</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>TR+PI+C/PI</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="11" t="n"/>
-      <c r="R18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
+      <c r="R18" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="S18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>501008903AA</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>后围加强板</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>HC260Y</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>301</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>卷料</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n"/>
+      <c r="R19" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>钢板模</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="N20" s="11" t="n"/>
@@ -2456,22 +3181,50 @@
       <c r="R20" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="44">
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="D2:R2"/>
+    <mergeCell ref="K14:K18"/>
     <mergeCell ref="N5:P5"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="J10:J13"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="G14:G18"/>
+    <mergeCell ref="I14:I18"/>
     <mergeCell ref="S3:T3"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="M10:M13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="M14:M18"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D14:D18"/>
+    <mergeCell ref="H14:H18"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="S10:S13"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
+    <mergeCell ref="L14:L18"/>
     <mergeCell ref="S5:S6"/>
+    <mergeCell ref="L10:L13"/>
     <mergeCell ref="H5:M5"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="J14:J18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="E14:E18"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A10:A13"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="I10:I13"/>
     <mergeCell ref="R5:R6"/>
+    <mergeCell ref="K10:K13"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="S14:S18"/>
+    <mergeCell ref="D10:D13"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3138,73 +3891,584 @@
       <c r="AD8" s="29" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="29" t="n"/>
-      <c r="P9" s="29" t="n"/>
+      <c r="A9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>501008899AB</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>后围内板</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>DC01</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>370</v>
+      </c>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>条料</t>
+        </is>
+      </c>
+      <c r="K9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O9" s="29" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="P9" s="29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" s="29" t="n"/>
       <c r="R9" s="29" t="n"/>
       <c r="S9" s="29" t="n"/>
       <c r="T9" s="29" t="n"/>
       <c r="U9" s="29" t="n"/>
       <c r="V9" s="29" t="n"/>
-      <c r="X9" s="29" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="W9" s="29" t="n"/>
+      <c r="X9" s="29" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y9" s="29" t="inlineStr">
+        <is>
+          <t>铸造模</t>
+        </is>
+      </c>
+      <c r="Z9" s="29" t="n"/>
+      <c r="AA9" s="29" t="n"/>
+      <c r="AB9" s="29" t="n"/>
+      <c r="AC9" s="29" t="n"/>
+      <c r="AD9" s="29" t="n"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="32" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="32" t="n"/>
+      <c r="L10" s="32" t="n"/>
+      <c r="M10" s="32" t="n"/>
+      <c r="N10" s="29" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="O10" s="29" t="inlineStr">
+        <is>
+          <t>TR+CTR+CPI</t>
+        </is>
+      </c>
+      <c r="P10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="29" t="n"/>
+      <c r="R10" s="29" t="n"/>
+      <c r="S10" s="29" t="n"/>
+      <c r="T10" s="29" t="n"/>
+      <c r="U10" s="29" t="n"/>
+      <c r="V10" s="29" t="n"/>
+      <c r="W10" s="32" t="n"/>
+      <c r="X10" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="Y10" s="32" t="n"/>
+      <c r="Z10" s="29" t="n"/>
+      <c r="AA10" s="29" t="n"/>
+      <c r="AB10" s="29" t="n"/>
+      <c r="AC10" s="29" t="n"/>
+      <c r="AD10" s="29" t="n"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="32" t="n"/>
+      <c r="M11" s="32" t="n"/>
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="O11" s="29" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="P11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="29" t="n"/>
+      <c r="R11" s="29" t="n"/>
+      <c r="S11" s="29" t="n"/>
+      <c r="T11" s="29" t="n"/>
+      <c r="U11" s="29" t="n"/>
+      <c r="V11" s="29" t="n"/>
+      <c r="W11" s="32" t="n"/>
+      <c r="X11" s="29" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y11" s="32" t="n"/>
+      <c r="Z11" s="29" t="n"/>
+      <c r="AA11" s="29" t="n"/>
+      <c r="AB11" s="29" t="n"/>
+      <c r="AC11" s="29" t="n"/>
+      <c r="AD11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="29" t="inlineStr">
+        <is>
+          <t>OP40</t>
+        </is>
+      </c>
+      <c r="O12" s="29" t="inlineStr">
+        <is>
+          <t>TR+CTR+PI+CPI</t>
+        </is>
+      </c>
+      <c r="P12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="29" t="n"/>
+      <c r="S12" s="29" t="n"/>
+      <c r="T12" s="29" t="n"/>
+      <c r="U12" s="29" t="n"/>
+      <c r="V12" s="29" t="n"/>
+      <c r="W12" s="28" t="n"/>
+      <c r="X12" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="29" t="n"/>
+      <c r="AA12" s="29" t="n"/>
+      <c r="AB12" s="29" t="n"/>
+      <c r="AC12" s="29" t="n"/>
+      <c r="AD12" s="29" t="n"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>501008901AB</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>后围左连接板</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>HC180Y</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>860</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>520</v>
+      </c>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>条料</t>
+        </is>
+      </c>
+      <c r="K13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="29" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O13" s="29" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="P13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="29" t="n"/>
+      <c r="R13" s="29" t="n"/>
+      <c r="S13" s="29" t="n"/>
+      <c r="T13" s="29" t="n"/>
+      <c r="U13" s="29" t="n"/>
+      <c r="V13" s="29" t="n"/>
+      <c r="W13" s="29" t="n"/>
+      <c r="X13" s="29" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y13" s="29" t="inlineStr">
+        <is>
+          <t>铸造模</t>
+        </is>
+      </c>
+      <c r="Z13" s="29" t="n"/>
+      <c r="AA13" s="29" t="n"/>
+      <c r="AB13" s="29" t="n"/>
+      <c r="AC13" s="29" t="n"/>
+      <c r="AD13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="32" t="n"/>
+      <c r="K14" s="32" t="n"/>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="32" t="n"/>
+      <c r="N14" s="29" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="P14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="29" t="n"/>
+      <c r="R14" s="29" t="n"/>
+      <c r="S14" s="29" t="n"/>
+      <c r="T14" s="29" t="n"/>
+      <c r="U14" s="29" t="n"/>
+      <c r="V14" s="29" t="n"/>
+      <c r="W14" s="32" t="n"/>
+      <c r="X14" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="Y14" s="32" t="n"/>
+      <c r="Z14" s="29" t="n"/>
+      <c r="AA14" s="29" t="n"/>
+      <c r="AB14" s="29" t="n"/>
+      <c r="AC14" s="29" t="n"/>
+      <c r="AD14" s="29" t="n"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="32" t="n"/>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="32" t="n"/>
+      <c r="M15" s="32" t="n"/>
+      <c r="N15" s="29" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="O15" s="29" t="inlineStr">
+        <is>
+          <t>TR+C/TR+SEP</t>
+        </is>
+      </c>
+      <c r="P15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="29" t="n"/>
+      <c r="S15" s="29" t="n"/>
+      <c r="T15" s="29" t="n"/>
+      <c r="U15" s="29" t="n"/>
+      <c r="V15" s="29" t="n"/>
+      <c r="W15" s="32" t="n"/>
+      <c r="X15" s="29" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y15" s="32" t="n"/>
+      <c r="Z15" s="29" t="n"/>
+      <c r="AA15" s="29" t="n"/>
+      <c r="AB15" s="29" t="n"/>
+      <c r="AC15" s="29" t="n"/>
+      <c r="AD15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="32" t="n"/>
+      <c r="J16" s="32" t="n"/>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n"/>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="29" t="inlineStr">
+        <is>
+          <t>OP40</t>
+        </is>
+      </c>
+      <c r="O16" s="29" t="inlineStr">
+        <is>
+          <t>FL+U/FL+RST</t>
+        </is>
+      </c>
+      <c r="P16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="29" t="n"/>
+      <c r="S16" s="29" t="n"/>
+      <c r="T16" s="29" t="n"/>
+      <c r="U16" s="29" t="n"/>
+      <c r="V16" s="29" t="n"/>
+      <c r="W16" s="32" t="n"/>
+      <c r="X16" s="29" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y16" s="32" t="n"/>
+      <c r="Z16" s="29" t="n"/>
+      <c r="AA16" s="29" t="n"/>
+      <c r="AB16" s="29" t="n"/>
+      <c r="AC16" s="29" t="n"/>
+      <c r="AD16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="29" t="inlineStr">
+        <is>
+          <t>OP50</t>
+        </is>
+      </c>
+      <c r="O17" s="29" t="inlineStr">
+        <is>
+          <t>TR+PI+C/PI</t>
+        </is>
+      </c>
+      <c r="P17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="29" t="n"/>
+      <c r="R17" s="29" t="n"/>
+      <c r="S17" s="29" t="n"/>
+      <c r="T17" s="29" t="n"/>
+      <c r="U17" s="29" t="n"/>
+      <c r="V17" s="29" t="n"/>
+      <c r="W17" s="28" t="n"/>
+      <c r="X17" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="Y17" s="28" t="n"/>
+      <c r="Z17" s="29" t="n"/>
+      <c r="AA17" s="29" t="n"/>
+      <c r="AB17" s="29" t="n"/>
+      <c r="AC17" s="29" t="n"/>
+      <c r="AD17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>501008903AA</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>后围加强板</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>HC260Y</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>301</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>180</v>
+      </c>
+      <c r="J18" s="29" t="inlineStr">
+        <is>
+          <t>卷料</t>
+        </is>
+      </c>
+      <c r="K18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="29" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="29" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="O18" s="29" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="P18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="29" t="n"/>
+      <c r="S18" s="29" t="n"/>
+      <c r="T18" s="29" t="n"/>
+      <c r="U18" s="29" t="n"/>
+      <c r="V18" s="29" t="n"/>
+      <c r="W18" s="29" t="n"/>
+      <c r="X18" s="29" t="n">
+        <v>315</v>
+      </c>
+      <c r="Y18" s="29" t="inlineStr">
+        <is>
+          <t>钢板模</t>
+        </is>
+      </c>
+      <c r="Z18" s="29" t="n"/>
+      <c r="AA18" s="29" t="n"/>
+      <c r="AB18" s="29" t="n"/>
+      <c r="AC18" s="29" t="n"/>
+      <c r="AD18" s="29" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>【模具费分摊说明】上传只读上方表格，不读本段。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>1. 先选采购基地并填写项目（新项目在本页填写）。模具方式或生产方式含「双槽 / 合并 / 一出二」→ 各序默认分摊 0.50；否则 1.00（单干）。左右件各记一半，避免同一副模记两次。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>2. 共模件若第一序单独开模（常见落料），上传后到模具清单把该序比例改成 1，后面共模序保持 0.50。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>3. 级进模写在生产方式。模具费不打 0.80（那是加工费折扣）。级进且共模仍是 0.50。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>4. 模具编号可空，系统按 DP-40-项目-流水自动补号；已填写的编号保持不变。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>5. 预估重量（T）= 长×宽×高×掏空×7.85÷10⁹。工序费 = 重量 × 单价 × 分摊比例 ÷ 分摊万台。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -3221,43 +4485,73 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="66">
     <mergeCell ref="AD1:AD2"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="H13:H17"/>
     <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="Y13:Y17"/>
+    <mergeCell ref="A25:AD25"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="C9:C12"/>
     <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="A12:AD12"/>
-    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="I13:I17"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="K13:K17"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="A13:A17"/>
     <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="A14:AD14"/>
+    <mergeCell ref="A20:AD20"/>
+    <mergeCell ref="J13:J17"/>
+    <mergeCell ref="W9:W12"/>
+    <mergeCell ref="L13:L17"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="L9:L12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="H3:AD3"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="M13:M17"/>
+    <mergeCell ref="A24:AD24"/>
+    <mergeCell ref="K9:K12"/>
+    <mergeCell ref="M9:M12"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="Y9:Y12"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="A21:AD21"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="W13:W17"/>
+    <mergeCell ref="A23:AD23"/>
+    <mergeCell ref="A22:AD22"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="X4:X5"/>
     <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="N4:P4"/>
     <mergeCell ref="AB1:AC2"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="A13:AD13"/>
-    <mergeCell ref="A10:AD10"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="G13:G17"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="W4:W5"/>
-    <mergeCell ref="H3:AD3"/>
-    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="A15:AD15"/>
-    <mergeCell ref="A11:AD11"/>
+    <mergeCell ref="B13:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
